--- a/Team-Data/2013-14/3-3-2013-14.xlsx
+++ b/Team-Data/2013-14/3-3-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,13 +818,13 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
         <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -778,7 +845,7 @@
         <v>22</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -796,7 +863,7 @@
         <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="n">
         <v>27</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>26</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -981,10 +1048,10 @@
         <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
@@ -1043,10 +1110,10 @@
         <v>35.3</v>
       </c>
       <c r="J4" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
         <v>8</v>
@@ -1055,13 +1122,13 @@
         <v>22.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O4" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P4" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0.762</v>
@@ -1070,25 +1137,25 @@
         <v>9.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T4" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="U4" t="n">
         <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="X4" t="n">
         <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z4" t="n">
         <v>21.8</v>
@@ -1100,16 +1167,16 @@
         <v>97.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.8</v>
+        <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>16</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
         <v>16</v>
@@ -1118,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="AI4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
@@ -1133,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>8</v>
@@ -1160,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>27</v>
@@ -1169,16 +1236,16 @@
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
         <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>0.45</v>
+        <v>0.458</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J5" t="n">
         <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P5" t="n">
         <v>25.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="R5" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T5" t="n">
         <v>42</v>
       </c>
       <c r="U5" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V5" t="n">
         <v>12.6</v>
@@ -1267,37 +1334,37 @@
         <v>6.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
         <v>18.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.2</v>
+        <v>95</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
       </c>
       <c r="AF5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1324,7 +1391,7 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
@@ -1336,7 +1403,7 @@
         <v>22</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1348,10 +1415,10 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>9</v>
@@ -1360,7 +1427,7 @@
         <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -1389,31 +1456,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
         <v>33</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.55</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.429</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
         <v>17.6</v>
@@ -1422,13 +1489,13 @@
         <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P6" t="n">
         <v>23.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R6" t="n">
         <v>12.1</v>
@@ -1437,19 +1504,19 @@
         <v>33.1</v>
       </c>
       <c r="T6" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U6" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="V6" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>6.2</v>
@@ -1458,28 +1525,28 @@
         <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>12</v>
       </c>
-      <c r="AF6" t="n">
-        <v>13</v>
-      </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1521,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -1655,10 +1722,10 @@
         <v>20</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>15</v>
@@ -1688,7 +1755,7 @@
         <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
         <v>18</v>
@@ -1900,10 +1967,10 @@
         <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
         <v>25</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.424</v>
+        <v>0.431</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J9" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="N9" t="n">
         <v>0.357</v>
       </c>
       <c r="O9" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.716</v>
+        <v>0.717</v>
       </c>
       <c r="R9" t="n">
         <v>12.5</v>
@@ -1983,7 +2050,7 @@
         <v>32.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U9" t="n">
         <v>21.6</v>
@@ -1998,22 +2065,22 @@
         <v>5.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
         <v>21.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.6</v>
+        <v>102.2</v>
       </c>
       <c r="AC9" t="n">
         <v>-2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2028,16 +2095,16 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2067,7 +2134,7 @@
         <v>14</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2079,7 +2146,7 @@
         <v>23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2138,34 +2205,34 @@
         <v>86.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L10" t="n">
         <v>5.9</v>
       </c>
       <c r="M10" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.312</v>
       </c>
       <c r="O10" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
         <v>25.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.668</v>
+        <v>0.666</v>
       </c>
       <c r="R10" t="n">
         <v>14.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="U10" t="n">
         <v>20.9</v>
@@ -2174,7 +2241,7 @@
         <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>5.2</v>
@@ -2183,34 +2250,34 @@
         <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.9</v>
+        <v>101</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="n">
         <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2243,7 +2310,7 @@
         <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>20</v>
@@ -2258,13 +2325,13 @@
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,13 +2456,13 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
@@ -2407,13 +2474,13 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO11" t="n">
         <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>23</v>
@@ -2431,13 +2498,13 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>4.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>15</v>
@@ -2616,16 +2683,16 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>5</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>7.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
         <v>21</v>
@@ -2771,7 +2838,7 @@
         <v>23</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -2947,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
         <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="K15" t="n">
         <v>0.448</v>
@@ -3054,19 +3121,19 @@
         <v>9.4</v>
       </c>
       <c r="M15" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O15" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P15" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R15" t="n">
         <v>9.199999999999999</v>
@@ -3075,16 +3142,16 @@
         <v>32.6</v>
       </c>
       <c r="T15" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U15" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X15" t="n">
         <v>5.8</v>
@@ -3096,25 +3163,25 @@
         <v>20.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.3</v>
+        <v>-5.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3129,10 +3196,10 @@
         <v>17</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN15" t="n">
         <v>3</v>
@@ -3141,10 +3208,10 @@
         <v>21</v>
       </c>
       <c r="AP15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3162,13 +3229,13 @@
         <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
         <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16" t="n">
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.576</v>
+        <v>0.569</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J16" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
@@ -3239,28 +3306,28 @@
         <v>14.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="P16" t="n">
         <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R16" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S16" t="n">
         <v>30.8</v>
       </c>
       <c r="T16" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
@@ -3281,13 +3348,13 @@
         <v>18.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC16" t="n">
         <v>0.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3302,13 +3369,13 @@
         <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="n">
         <v>13</v>
@@ -3350,7 +3417,7 @@
         <v>17</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -3391,37 +3458,37 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.754</v>
+        <v>0.75</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J17" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="K17" t="n">
         <v>0.511</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.373</v>
+        <v>0.369</v>
       </c>
       <c r="O17" t="n">
         <v>17.9</v>
@@ -3442,37 +3509,37 @@
         <v>36.8</v>
       </c>
       <c r="U17" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W17" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>4.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="n">
         <v>20.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.7</v>
+        <v>104.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AD17" t="n">
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
@@ -3499,7 +3566,7 @@
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
         <v>14</v>
@@ -3523,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
@@ -3535,13 +3602,13 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -3573,58 +3640,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
         <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>0.203</v>
+        <v>0.19</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.429</v>
+        <v>0.426</v>
       </c>
       <c r="L18" t="n">
         <v>7.4</v>
       </c>
       <c r="M18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O18" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P18" t="n">
         <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R18" t="n">
         <v>11.7</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V18" t="n">
         <v>15.5</v>
@@ -3642,16 +3709,16 @@
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,10 +3733,10 @@
         <v>6</v>
       </c>
       <c r="AI18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3678,10 +3745,10 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
         <v>28</v>
@@ -3690,7 +3757,7 @@
         <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
         <v>12</v>
@@ -3702,13 +3769,13 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3717,7 +3784,7 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19" t="n">
         <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>38.5</v>
       </c>
       <c r="J19" t="n">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.439</v>
@@ -3782,19 +3849,19 @@
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O19" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R19" t="n">
         <v>12.8</v>
@@ -3809,13 +3876,13 @@
         <v>23.3</v>
       </c>
       <c r="V19" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W19" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y19" t="n">
         <v>5.8</v>
@@ -3824,22 +3891,22 @@
         <v>18.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.2</v>
+        <v>105.7</v>
       </c>
       <c r="AC19" t="n">
         <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>15</v>
@@ -3851,16 +3918,16 @@
         <v>11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
       </c>
       <c r="AL19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN19" t="n">
         <v>27</v>
@@ -3872,19 +3939,19 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV19" t="n">
         <v>6</v>
@@ -3899,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -3937,58 +4004,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>0.383</v>
+        <v>0.39</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J20" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L20" t="n">
         <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O20" t="n">
         <v>17.2</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U20" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V20" t="n">
         <v>13.9</v>
@@ -4000,46 +4067,46 @@
         <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC20" t="n">
         <v>-2.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG20" t="n">
         <v>21</v>
       </c>
-      <c r="AG20" t="n">
-        <v>22</v>
-      </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
         <v>14</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
@@ -4057,16 +4124,16 @@
         <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4081,7 +4148,7 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -4119,34 +4186,34 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>0.344</v>
+        <v>0.35</v>
       </c>
       <c r="H21" t="n">
         <v>48.6</v>
       </c>
       <c r="I21" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J21" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L21" t="n">
         <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N21" t="n">
         <v>0.365</v>
@@ -4155,22 +4222,22 @@
         <v>14.8</v>
       </c>
       <c r="P21" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T21" t="n">
         <v>40.9</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
         <v>13.2</v>
@@ -4188,28 +4255,28 @@
         <v>22.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4218,13 +4285,13 @@
         <v>13</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN21" t="n">
         <v>11</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4257,7 +4324,7 @@
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4266,10 +4333,10 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4388,13 +4455,13 @@
         <v>3</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
         <v>20</v>
@@ -4403,13 +4470,13 @@
         <v>4</v>
       </c>
       <c r="AL22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM22" t="n">
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4427,7 +4494,7 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>15</v>
@@ -4436,7 +4503,7 @@
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,7 +4512,7 @@
         <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4646,7 @@
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
@@ -4606,7 +4673,7 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI24" t="n">
         <v>12</v>
@@ -4770,7 +4837,7 @@
         <v>23</v>
       </c>
       <c r="AM24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN24" t="n">
         <v>30</v>
@@ -4809,10 +4876,10 @@
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB24" t="n">
         <v>18</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4946,7 +5013,7 @@
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>4</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
         <v>41</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="J26" t="n">
-        <v>87.8</v>
+        <v>87.7</v>
       </c>
       <c r="K26" t="n">
         <v>0.452</v>
@@ -5059,31 +5126,31 @@
         <v>24.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.823</v>
+        <v>0.826</v>
       </c>
       <c r="R26" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S26" t="n">
         <v>33.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
         <v>23.5</v>
       </c>
       <c r="V26" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W26" t="n">
         <v>5.6</v>
@@ -5095,7 +5162,7 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA26" t="n">
         <v>20.6</v>
@@ -5107,7 +5174,7 @@
         <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5119,13 +5186,13 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>14</v>
@@ -5137,10 +5204,10 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
@@ -5176,7 +5243,7 @@
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -5211,49 +5278,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
         <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J27" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.448</v>
       </c>
       <c r="L27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M27" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O27" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="P27" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0.777</v>
       </c>
       <c r="R27" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S27" t="n">
         <v>31.7</v>
@@ -5262,10 +5329,10 @@
         <v>43.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="V27" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W27" t="n">
         <v>7.4</v>
@@ -5277,28 +5344,28 @@
         <v>5.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.5</v>
+        <v>101.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>12</v>
@@ -5307,7 +5374,7 @@
         <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK27" t="n">
         <v>18</v>
@@ -5316,7 +5383,7 @@
         <v>24</v>
       </c>
       <c r="AM27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN27" t="n">
         <v>26</v>
@@ -5328,10 +5395,10 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
         <v>16</v>
@@ -5346,7 +5413,7 @@
         <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX27" t="n">
         <v>28</v>
@@ -5355,7 +5422,7 @@
         <v>24</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5498,7 +5565,7 @@
         <v>13</v>
       </c>
       <c r="AM28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5513,7 +5580,7 @@
         <v>4</v>
       </c>
       <c r="AR28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
@@ -5525,16 +5592,16 @@
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF29" t="n">
         <v>12</v>
@@ -5671,7 +5738,7 @@
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
@@ -5686,13 +5753,13 @@
         <v>12</v>
       </c>
       <c r="AO29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP29" t="n">
         <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
         <v>10</v>
@@ -5719,7 +5786,7 @@
         <v>12</v>
       </c>
       <c r="AZ29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
-        <v>0.35</v>
+        <v>0.356</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.442</v>
@@ -5784,31 +5851,31 @@
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N30" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O30" t="n">
         <v>16.3</v>
       </c>
       <c r="P30" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
         <v>41.5</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V30" t="n">
         <v>14.6</v>
@@ -5829,13 +5896,13 @@
         <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>-5.9</v>
+        <v>-5.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
@@ -5856,13 +5923,13 @@
         <v>26</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="n">
         <v>22</v>
       </c>
       <c r="AM30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN30" t="n">
         <v>17</v>
@@ -5874,7 +5941,7 @@
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR30" t="n">
         <v>20</v>
@@ -5892,7 +5959,7 @@
         <v>13</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX30" t="n">
         <v>16</v>
@@ -5901,7 +5968,7 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="n">
         <v>31</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.517</v>
+        <v>0.525</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J31" t="n">
         <v>84.90000000000001</v>
@@ -5963,40 +6030,40 @@
         <v>0.454</v>
       </c>
       <c r="L31" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M31" t="n">
         <v>20.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.383</v>
+        <v>0.382</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
         <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T31" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U31" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="V31" t="n">
         <v>14.7</v>
       </c>
       <c r="W31" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X31" t="n">
         <v>4.8</v>
@@ -6008,16 +6075,16 @@
         <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB31" t="n">
         <v>100.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6038,13 +6105,13 @@
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
       </c>
       <c r="AM31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN31" t="n">
         <v>2</v>
@@ -6056,10 +6123,10 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS31" t="n">
         <v>18</v>
@@ -6068,13 +6135,13 @@
         <v>17</v>
       </c>
       <c r="AU31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>14</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-3-2013-14</t>
+          <t>2014-03-03</t>
         </is>
       </c>
     </row>
